--- a/hotfix/add-interop-link-in-note/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
+++ b/hotfix/add-interop-link-in-note/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T06:47:28+00:00</t>
+    <t>2024-07-17T06:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
